--- a/Mod_Korean/Lang/KR/Game/Category.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Category.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="570">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">new</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.338 Patch 2</t>
+    <t xml:space="preserve">EA 23.352</t>
   </si>
   <si>
     <t xml:space="preserve">New Items</t>
@@ -822,6 +822,15 @@
   </si>
   <si>
     <t xml:space="preserve">光源</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">遺物</t>
   </si>
   <si>
     <t xml:space="preserve">furniture</t>
@@ -1806,10 +1815,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -1823,10 +1832,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1840,10 +1849,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C5" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -1857,10 +1866,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1874,10 +1883,10 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -1891,10 +1900,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
@@ -1908,10 +1917,10 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C9" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -1925,10 +1934,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C10" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D10" t="s">
         <v>26</v>
@@ -1942,10 +1951,10 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C11" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -1959,10 +1968,10 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C12" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -1976,10 +1985,10 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C13" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D13" t="s">
         <v>35</v>
@@ -1993,7 +2002,7 @@
         <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C14" t="s">
         <v>38</v>
@@ -2010,10 +2019,10 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C15" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D15" t="s">
         <v>40</v>
@@ -2027,10 +2036,10 @@
         <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C16" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D16" t="s">
         <v>43</v>
@@ -2044,10 +2053,10 @@
         <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C17" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D17" t="s">
         <v>43</v>
@@ -2061,10 +2070,10 @@
         <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C18" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D18" t="s">
         <v>47</v>
@@ -2078,10 +2087,10 @@
         <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C19" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D19" t="s">
         <v>50</v>
@@ -2095,10 +2104,10 @@
         <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C20" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D20" t="s">
         <v>53</v>
@@ -2112,10 +2121,10 @@
         <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C21" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D21" t="s">
         <v>56</v>
@@ -2129,10 +2138,10 @@
         <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C22" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D22" t="s">
         <v>59</v>
@@ -2146,10 +2155,10 @@
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C23" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D23" t="s">
         <v>62</v>
@@ -2163,10 +2172,10 @@
         <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C24" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D24" t="s">
         <v>65</v>
@@ -2180,10 +2189,10 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C25" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D25" t="s">
         <v>68</v>
@@ -2197,10 +2206,10 @@
         <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C26" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D26" t="s">
         <v>71</v>
@@ -2214,10 +2223,10 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C27" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D27" t="s">
         <v>74</v>
@@ -2231,10 +2240,10 @@
         <v>76</v>
       </c>
       <c r="B28" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C28" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D28" t="s">
         <v>77</v>
@@ -2248,10 +2257,10 @@
         <v>79</v>
       </c>
       <c r="B29" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C29" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D29" t="s">
         <v>80</v>
@@ -2265,10 +2274,10 @@
         <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C30" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D30" t="s">
         <v>83</v>
@@ -2282,10 +2291,10 @@
         <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C31" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D31" t="s">
         <v>86</v>
@@ -2299,10 +2308,10 @@
         <v>88</v>
       </c>
       <c r="B32" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C32" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D32" t="s">
         <v>89</v>
@@ -2316,10 +2325,10 @@
         <v>91</v>
       </c>
       <c r="B33" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C33" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D33" t="s">
         <v>92</v>
@@ -2333,10 +2342,10 @@
         <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C34" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D34" t="s">
         <v>95</v>
@@ -2350,10 +2359,10 @@
         <v>97</v>
       </c>
       <c r="B35" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C35" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D35" t="s">
         <v>98</v>
@@ -2367,10 +2376,10 @@
         <v>100</v>
       </c>
       <c r="B36" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C36" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D36" t="s">
         <v>101</v>
@@ -2384,10 +2393,10 @@
         <v>103</v>
       </c>
       <c r="B37" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C37" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D37" t="s">
         <v>104</v>
@@ -2401,10 +2410,10 @@
         <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C38" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D38" t="s">
         <v>107</v>
@@ -2418,10 +2427,10 @@
         <v>109</v>
       </c>
       <c r="B39" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C39" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D39" t="s">
         <v>110</v>
@@ -2435,10 +2444,10 @@
         <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C40" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D40" t="s">
         <v>113</v>
@@ -2452,10 +2461,10 @@
         <v>115</v>
       </c>
       <c r="B41" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C41" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D41" t="s">
         <v>116</v>
@@ -2469,10 +2478,10 @@
         <v>118</v>
       </c>
       <c r="B42" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C42" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D42" t="s">
         <v>119</v>
@@ -2486,10 +2495,10 @@
         <v>121</v>
       </c>
       <c r="B43" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C43" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D43" t="s">
         <v>122</v>
@@ -2503,10 +2512,10 @@
         <v>124</v>
       </c>
       <c r="B44" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C44" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D44" t="s">
         <v>125</v>
@@ -2520,10 +2529,10 @@
         <v>127</v>
       </c>
       <c r="B45" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C45" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D45" t="s">
         <v>128</v>
@@ -2537,10 +2546,10 @@
         <v>130</v>
       </c>
       <c r="B46" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C46" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D46" t="s">
         <v>131</v>
@@ -2554,10 +2563,10 @@
         <v>133</v>
       </c>
       <c r="B47" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C47" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D47" t="s">
         <v>134</v>
@@ -2571,10 +2580,10 @@
         <v>136</v>
       </c>
       <c r="B48" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C48" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D48" t="s">
         <v>137</v>
@@ -2588,10 +2597,10 @@
         <v>139</v>
       </c>
       <c r="B49" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C49" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D49" t="s">
         <v>140</v>
@@ -2605,10 +2614,10 @@
         <v>142</v>
       </c>
       <c r="B50" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C50" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D50" t="s">
         <v>143</v>
@@ -2622,10 +2631,10 @@
         <v>145</v>
       </c>
       <c r="B51" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C51" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D51" t="s">
         <v>143</v>
@@ -2639,10 +2648,10 @@
         <v>146</v>
       </c>
       <c r="B52" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C52" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D52" t="s">
         <v>147</v>
@@ -2656,10 +2665,10 @@
         <v>149</v>
       </c>
       <c r="B53" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C53" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D53" t="s">
         <v>150</v>
@@ -2673,10 +2682,10 @@
         <v>152</v>
       </c>
       <c r="B54" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C54" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D54" t="s">
         <v>153</v>
@@ -2690,10 +2699,10 @@
         <v>155</v>
       </c>
       <c r="B55" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C55" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D55" t="s">
         <v>156</v>
@@ -2707,10 +2716,10 @@
         <v>158</v>
       </c>
       <c r="B56" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C56" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D56" t="s">
         <v>159</v>
@@ -2724,10 +2733,10 @@
         <v>161</v>
       </c>
       <c r="B57" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C57" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D57" t="s">
         <v>162</v>
@@ -2741,10 +2750,10 @@
         <v>164</v>
       </c>
       <c r="B58" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C58" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D58" t="s">
         <v>165</v>
@@ -2758,10 +2767,10 @@
         <v>167</v>
       </c>
       <c r="B59" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C59" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D59" t="s">
         <v>168</v>
@@ -2775,10 +2784,10 @@
         <v>170</v>
       </c>
       <c r="B60" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C60" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D60" t="s">
         <v>171</v>
@@ -2792,10 +2801,10 @@
         <v>173</v>
       </c>
       <c r="B61" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C61" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D61" t="s">
         <v>174</v>
@@ -2809,10 +2818,10 @@
         <v>176</v>
       </c>
       <c r="B62" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C62" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D62" t="s">
         <v>177</v>
@@ -2826,10 +2835,10 @@
         <v>179</v>
       </c>
       <c r="B63" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C63" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D63" t="s">
         <v>180</v>
@@ -2843,10 +2852,10 @@
         <v>182</v>
       </c>
       <c r="B64" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C64" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D64" t="s">
         <v>183</v>
@@ -2860,10 +2869,10 @@
         <v>185</v>
       </c>
       <c r="B65" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C65" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D65" t="s">
         <v>186</v>
@@ -2877,10 +2886,10 @@
         <v>188</v>
       </c>
       <c r="B66" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C66" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D66" t="s">
         <v>189</v>
@@ -2894,10 +2903,10 @@
         <v>191</v>
       </c>
       <c r="B67" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C67" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D67" t="s">
         <v>192</v>
@@ -2911,10 +2920,10 @@
         <v>194</v>
       </c>
       <c r="B68" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C68" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D68" t="s">
         <v>195</v>
@@ -2928,10 +2937,10 @@
         <v>197</v>
       </c>
       <c r="B69" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C69" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D69" t="s">
         <v>198</v>
@@ -2945,10 +2954,10 @@
         <v>200</v>
       </c>
       <c r="B70" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C70" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D70" t="s">
         <v>201</v>
@@ -2962,10 +2971,10 @@
         <v>203</v>
       </c>
       <c r="B71" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C71" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D71" t="s">
         <v>204</v>
@@ -2979,10 +2988,10 @@
         <v>206</v>
       </c>
       <c r="B72" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C72" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D72" t="s">
         <v>207</v>
@@ -2996,10 +3005,10 @@
         <v>209</v>
       </c>
       <c r="B73" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C73" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D73" t="s">
         <v>210</v>
@@ -3013,10 +3022,10 @@
         <v>212</v>
       </c>
       <c r="B74" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C74" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D74" t="s">
         <v>213</v>
@@ -3030,10 +3039,10 @@
         <v>215</v>
       </c>
       <c r="B75" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C75" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D75" t="s">
         <v>216</v>
@@ -3047,10 +3056,10 @@
         <v>218</v>
       </c>
       <c r="B76" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C76" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D76" t="s">
         <v>219</v>
@@ -3064,10 +3073,10 @@
         <v>221</v>
       </c>
       <c r="B77" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C77" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D77" t="s">
         <v>222</v>
@@ -3081,10 +3090,10 @@
         <v>224</v>
       </c>
       <c r="B78" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C78" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D78" t="s">
         <v>225</v>
@@ -3098,10 +3107,10 @@
         <v>227</v>
       </c>
       <c r="B79" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C79" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D79" t="s">
         <v>228</v>
@@ -3115,10 +3124,10 @@
         <v>230</v>
       </c>
       <c r="B80" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C80" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D80" t="s">
         <v>231</v>
@@ -3132,10 +3141,10 @@
         <v>233</v>
       </c>
       <c r="B81" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C81" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D81" t="s">
         <v>234</v>
@@ -3149,10 +3158,10 @@
         <v>236</v>
       </c>
       <c r="B82" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C82" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D82" t="s">
         <v>237</v>
@@ -3166,10 +3175,10 @@
         <v>239</v>
       </c>
       <c r="B83" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C83" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D83" t="s">
         <v>240</v>
@@ -3183,10 +3192,10 @@
         <v>242</v>
       </c>
       <c r="B84" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C84" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D84" t="s">
         <v>243</v>
@@ -3200,10 +3209,10 @@
         <v>245</v>
       </c>
       <c r="B85" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C85" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D85" t="s">
         <v>246</v>
@@ -3217,10 +3226,10 @@
         <v>248</v>
       </c>
       <c r="B86" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C86" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D86" t="s">
         <v>249</v>
@@ -3234,10 +3243,10 @@
         <v>251</v>
       </c>
       <c r="B87" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C87" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D87" t="s">
         <v>252</v>
@@ -3251,10 +3260,10 @@
         <v>254</v>
       </c>
       <c r="B88" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C88" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D88" t="s">
         <v>255</v>
@@ -3268,10 +3277,10 @@
         <v>257</v>
       </c>
       <c r="B89" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C89" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D89" t="s">
         <v>258</v>
@@ -3285,10 +3294,10 @@
         <v>260</v>
       </c>
       <c r="B90" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C90" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D90" t="s">
         <v>261</v>
@@ -3302,10 +3311,10 @@
         <v>263</v>
       </c>
       <c r="B91" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C91" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D91" t="s">
         <v>264</v>
@@ -3319,10 +3328,10 @@
         <v>266</v>
       </c>
       <c r="B92" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C92" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D92" t="s">
         <v>267</v>
@@ -3336,10 +3345,7 @@
         <v>269</v>
       </c>
       <c r="B93" t="s">
-        <v>411</v>
-      </c>
-      <c r="C93" t="s">
-        <v>521</v>
+        <v>6</v>
       </c>
       <c r="D93" t="s">
         <v>270</v>
@@ -3353,33 +3359,33 @@
         <v>272</v>
       </c>
       <c r="B94" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C94" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D94" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E94" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>275</v>
+      </c>
+      <c r="B95" t="s">
+        <v>415</v>
+      </c>
+      <c r="C95" t="s">
+        <v>524</v>
+      </c>
+      <c r="D95" t="s">
         <v>273</v>
       </c>
-      <c r="B95" t="s">
-        <v>411</v>
-      </c>
-      <c r="C95" t="s">
-        <v>522</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>274</v>
-      </c>
-      <c r="E95" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="96">
@@ -3387,10 +3393,10 @@
         <v>276</v>
       </c>
       <c r="B96" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C96" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D96" t="s">
         <v>277</v>
@@ -3404,10 +3410,10 @@
         <v>279</v>
       </c>
       <c r="B97" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C97" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D97" t="s">
         <v>280</v>
@@ -3421,10 +3427,10 @@
         <v>282</v>
       </c>
       <c r="B98" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C98" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D98" t="s">
         <v>283</v>
@@ -3438,10 +3444,10 @@
         <v>285</v>
       </c>
       <c r="B99" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C99" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D99" t="s">
         <v>286</v>
@@ -3455,10 +3461,10 @@
         <v>288</v>
       </c>
       <c r="B100" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C100" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D100" t="s">
         <v>289</v>
@@ -3472,10 +3478,10 @@
         <v>291</v>
       </c>
       <c r="B101" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="C101" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D101" t="s">
         <v>292</v>
@@ -3489,10 +3495,10 @@
         <v>294</v>
       </c>
       <c r="B102" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C102" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D102" t="s">
         <v>295</v>
@@ -3506,10 +3512,10 @@
         <v>297</v>
       </c>
       <c r="B103" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C103" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D103" t="s">
         <v>298</v>
@@ -3523,10 +3529,10 @@
         <v>300</v>
       </c>
       <c r="B104" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="C104" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D104" t="s">
         <v>301</v>
@@ -3540,10 +3546,10 @@
         <v>303</v>
       </c>
       <c r="B105" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="C105" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D105" t="s">
         <v>304</v>
@@ -3557,10 +3563,10 @@
         <v>306</v>
       </c>
       <c r="B106" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="C106" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D106" t="s">
         <v>307</v>
@@ -3574,10 +3580,10 @@
         <v>309</v>
       </c>
       <c r="B107" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="C107" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D107" t="s">
         <v>310</v>
@@ -3591,10 +3597,10 @@
         <v>312</v>
       </c>
       <c r="B108" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="C108" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D108" t="s">
         <v>313</v>
@@ -3608,10 +3614,10 @@
         <v>315</v>
       </c>
       <c r="B109" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C109" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D109" t="s">
         <v>316</v>
@@ -3625,10 +3631,10 @@
         <v>318</v>
       </c>
       <c r="B110" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C110" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D110" t="s">
         <v>319</v>
@@ -3642,10 +3648,10 @@
         <v>321</v>
       </c>
       <c r="B111" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C111" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D111" t="s">
         <v>322</v>
@@ -3659,10 +3665,10 @@
         <v>324</v>
       </c>
       <c r="B112" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C112" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D112" t="s">
         <v>325</v>
@@ -3676,10 +3682,10 @@
         <v>327</v>
       </c>
       <c r="B113" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="C113" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D113" t="s">
         <v>328</v>
@@ -3693,10 +3699,10 @@
         <v>330</v>
       </c>
       <c r="B114" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="C114" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D114" t="s">
         <v>331</v>
@@ -3710,33 +3716,33 @@
         <v>333</v>
       </c>
       <c r="B115" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C115" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D115" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E115" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
+        <v>336</v>
+      </c>
+      <c r="B116" t="s">
+        <v>415</v>
+      </c>
+      <c r="C116" t="s">
+        <v>544</v>
+      </c>
+      <c r="D116" t="s">
         <v>334</v>
       </c>
-      <c r="B116" t="s">
-        <v>431</v>
-      </c>
-      <c r="C116" t="s">
-        <v>542</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>335</v>
-      </c>
-      <c r="E116" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="117">
@@ -3744,10 +3750,10 @@
         <v>337</v>
       </c>
       <c r="B117" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C117" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D117" t="s">
         <v>338</v>
@@ -3761,10 +3767,10 @@
         <v>340</v>
       </c>
       <c r="B118" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="C118" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D118" t="s">
         <v>341</v>
@@ -3778,10 +3784,10 @@
         <v>343</v>
       </c>
       <c r="B119" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C119" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D119" t="s">
         <v>344</v>
@@ -3795,33 +3801,33 @@
         <v>346</v>
       </c>
       <c r="B120" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C120" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D120" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E120" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
+        <v>349</v>
+      </c>
+      <c r="B121" t="s">
+        <v>415</v>
+      </c>
+      <c r="C121" t="s">
+        <v>548</v>
+      </c>
+      <c r="D121" t="s">
         <v>347</v>
       </c>
-      <c r="B121" t="s">
-        <v>411</v>
-      </c>
-      <c r="C121" t="s">
-        <v>546</v>
-      </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
         <v>348</v>
-      </c>
-      <c r="E121" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="122">
@@ -3832,7 +3838,7 @@
         <v>414</v>
       </c>
       <c r="C122" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D122" t="s">
         <v>351</v>
@@ -3846,10 +3852,10 @@
         <v>353</v>
       </c>
       <c r="B123" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C123" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D123" t="s">
         <v>354</v>
@@ -3863,10 +3869,10 @@
         <v>356</v>
       </c>
       <c r="B124" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C124" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D124" t="s">
         <v>357</v>
@@ -3880,10 +3886,10 @@
         <v>359</v>
       </c>
       <c r="B125" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C125" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D125" t="s">
         <v>360</v>
@@ -3897,10 +3903,10 @@
         <v>362</v>
       </c>
       <c r="B126" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="C126" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D126" t="s">
         <v>363</v>
@@ -3914,10 +3920,10 @@
         <v>365</v>
       </c>
       <c r="B127" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="C127" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D127" t="s">
         <v>366</v>
@@ -3934,7 +3940,7 @@
         <v>414</v>
       </c>
       <c r="C128" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D128" t="s">
         <v>369</v>
@@ -3948,10 +3954,10 @@
         <v>371</v>
       </c>
       <c r="B129" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C129" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D129" t="s">
         <v>372</v>
@@ -3965,10 +3971,10 @@
         <v>374</v>
       </c>
       <c r="B130" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C130" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D130" t="s">
         <v>375</v>
@@ -3982,10 +3988,10 @@
         <v>377</v>
       </c>
       <c r="B131" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C131" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D131" t="s">
         <v>378</v>
@@ -3999,10 +4005,10 @@
         <v>380</v>
       </c>
       <c r="B132" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C132" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D132" t="s">
         <v>381</v>
@@ -4016,10 +4022,10 @@
         <v>383</v>
       </c>
       <c r="B133" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C133" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D133" t="s">
         <v>384</v>
@@ -4033,10 +4039,10 @@
         <v>386</v>
       </c>
       <c r="B134" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C134" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D134" t="s">
         <v>387</v>
@@ -4050,10 +4056,10 @@
         <v>389</v>
       </c>
       <c r="B135" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C135" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D135" t="s">
         <v>390</v>
@@ -4067,10 +4073,10 @@
         <v>392</v>
       </c>
       <c r="B136" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="C136" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D136" t="s">
         <v>393</v>
@@ -4084,10 +4090,10 @@
         <v>395</v>
       </c>
       <c r="B137" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="C137" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D137" t="s">
         <v>396</v>
@@ -4101,33 +4107,33 @@
         <v>398</v>
       </c>
       <c r="B138" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C138" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D138" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E138" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
+        <v>401</v>
+      </c>
+      <c r="B139" t="s">
+        <v>415</v>
+      </c>
+      <c r="C139" t="s">
+        <v>565</v>
+      </c>
+      <c r="D139" t="s">
         <v>399</v>
       </c>
-      <c r="B139" t="s">
-        <v>411</v>
-      </c>
-      <c r="C139" t="s">
-        <v>563</v>
-      </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>400</v>
-      </c>
-      <c r="E139" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="140">
@@ -4135,10 +4141,10 @@
         <v>402</v>
       </c>
       <c r="B140" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="C140" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D140" t="s">
         <v>403</v>
@@ -4152,10 +4158,10 @@
         <v>405</v>
       </c>
       <c r="B141" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C141" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D141" t="s">
         <v>406</v>
@@ -4169,16 +4175,33 @@
         <v>408</v>
       </c>
       <c r="B142" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="C142" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D142" t="s">
         <v>409</v>
       </c>
       <c r="E142" t="s">
         <v>410</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>411</v>
+      </c>
+      <c r="B143" t="s">
+        <v>414</v>
+      </c>
+      <c r="C143" t="s">
+        <v>569</v>
+      </c>
+      <c r="D143" t="s">
+        <v>412</v>
+      </c>
+      <c r="E143" t="s">
+        <v>413</v>
       </c>
     </row>
   </sheetData>
